--- a/results/link-prediction-gcn/Link/5shot/PTC_MR/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/PTC_MR/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5983±0.0208</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5912±0.0000</t>
+          <t>0.5972±0.0015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5900±0.0062</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5971±0.0000</t>
+          <t>0.5729±0.0297</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5905±0.0000</t>
+          <t>0.5548±0.0234</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6007±0.0000</t>
+          <t>0.5851±0.0320</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5835±0.0161</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5835±0.0161</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5835±0.0161</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.6002±0.0074</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5386±0.0000</t>
+          <t>0.5169±0.0231</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.5876±0.0135</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6012±0.0000</t>
+          <t>0.5979±0.0009</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5799±0.0000</t>
+          <t>0.5945±0.0041</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5614±0.0142</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.5961±0.0026</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5846±0.0000</t>
+          <t>0.5690±0.0327</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5988±0.0009</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5900±0.0118</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5900±0.0118</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5900±0.0118</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5988±0.0009</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6005±0.0000</t>
+          <t>0.5249±0.0201</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5943±0.0000</t>
+          <t>0.5988±0.0009</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.6012±0.0000</t>
+          <t>0.5376±0.0023</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5976±0.0009</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5893±0.0083</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6019±0.0000</t>
+          <t>0.5974±0.0003</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5986±0.0000</t>
+          <t>0.5891±0.0132</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.5708±0.0384</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5742±0.0329</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5742±0.0329</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5742±0.0329</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5846±0.0000</t>
+          <t>0.5471±0.0450</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5533±0.0000</t>
+          <t>0.5178±0.0103</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5558±0.0301</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.5573±0.0334</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.5862±0.0129</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5790±0.0121</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5934±0.0000</t>
+          <t>0.5751±0.0172</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5581±0.0000</t>
+          <t>0.5750±0.0370</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5647±0.0000</t>
+          <t>0.5237±0.0145</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5255±0.0000</t>
+          <t>0.5597±0.0081</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5255±0.0000</t>
+          <t>0.5597±0.0081</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5255±0.0000</t>
+          <t>0.5597±0.0081</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5511±0.0000</t>
+          <t>0.5460±0.0034</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5284±0.0000</t>
+          <t>0.5022±0.0061</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5421±0.0000</t>
+          <t>0.5809±0.0065</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5981±0.0000</t>
+          <t>0.6051±0.0081</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5974±0.0018</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5933±0.0091</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5981±0.0007</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5774±0.0268</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5992±0.0012</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5979±0.0009</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5979±0.0009</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5979±0.0009</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5902±0.0100</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5521±0.0000</t>
+          <t>0.5308±0.0438</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5915±0.0082</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5979±0.0009</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5945±0.0013</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5917±0.0048</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5749±0.0124</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5986±0.0012</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.6015±0.0029</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5943±0.0057</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5943±0.0057</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5943±0.0057</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.6005±0.0015</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5458±0.0000</t>
+          <t>0.5503±0.0064</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5992±0.0018</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0012</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5403±0.0000</t>
+          <t>0.5237±0.0073</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5465±0.0167</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.4680±0.0000</t>
+          <t>0.4959±0.0231</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.5906±0.0306</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5751±0.0279</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.5233±0.0116</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5349±0.0033</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5349±0.0033</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5349±0.0033</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5254±0.0000</t>
+          <t>0.5322±0.0105</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.5055±0.0109</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5296±0.0000</t>
+          <t>0.5271±0.0048</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7206±0.0296</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7477±0.0014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7346±0.0144</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7474±0.0000</t>
+          <t>0.7104±0.0189</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7426±0.0000</t>
+          <t>0.7012±0.0283</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7506±0.0000</t>
+          <t>0.7122±0.0448</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7076±0.0411</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7076±0.0411</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7076±0.0411</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7406±0.0078</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6326±0.0000</t>
+          <t>0.6019±0.0275</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7494±0.0000</t>
+          <t>0.7379±0.0131</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7509±0.0000</t>
+          <t>0.7483±0.0007</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7321±0.0000</t>
+          <t>0.7450±0.0042</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7001±0.0188</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7467±0.0024</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7367±0.0000</t>
+          <t>0.6780±0.0618</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7491±0.0007</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7263±0.0317</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7263±0.0317</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7263±0.0317</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7467±0.0000</t>
+          <t>0.7491±0.0007</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7504±0.0000</t>
+          <t>0.6391±0.0414</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7491±0.0007</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,62 +1490,62 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.7509±0.0000</t>
+          <t>0.6828±0.0056</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7480±0.0006</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7408±0.0071</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7515±0.0000</t>
+          <t>0.7478±0.0002</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.7489±0.0000</t>
+          <t>0.7191±0.0242</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7113±0.0525</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7187±0.0408</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7187±0.0408</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7187±0.0408</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.7379±0.0000</t>
+          <t>0.6851±0.0572</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6532±0.0000</t>
+          <t>0.6290±0.0142</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7069±0.0293</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1555,62 +1555,62 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7433±0.0000</t>
+          <t>0.6676±0.0641</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7190±0.0000</t>
+          <t>0.7381±0.0111</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7440±0.0000</t>
+          <t>0.7311±0.0105</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7256±0.0161</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7137±0.0000</t>
+          <t>0.7189±0.0318</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6871±0.0000</t>
+          <t>0.6489±0.0160</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6569±0.0000</t>
+          <t>0.6865±0.0040</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6569±0.0000</t>
+          <t>0.6865±0.0040</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6569±0.0000</t>
+          <t>0.6865±0.0040</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6764±0.0000</t>
+          <t>0.6561±0.0111</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.6280±0.0000</t>
+          <t>0.5809±0.0045</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.7100±0.0095</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7407±0.0125</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7476±0.0018</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7440±0.0079</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7485±0.0005</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7282±0.0267</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7472±0.0021</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7483±0.0007</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7483±0.0007</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7483±0.0007</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7402±0.0108</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6595±0.0000</t>
+          <t>0.6400±0.0639</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7429±0.0071</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7483±0.0007</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7454±0.0011</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7410±0.0069</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7466±0.0000</t>
+          <t>0.7273±0.0104</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7486±0.0009</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7480±0.0027</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7333±0.0218</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7333±0.0218</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7333±0.0218</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7454±0.0063</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6437±0.0000</t>
+          <t>0.6743±0.0097</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7480±0.0003</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6597±0.0069</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6560±0.0000</t>
+          <t>0.7013±0.0164</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6051±0.0000</t>
+          <t>0.6286±0.0354</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6859±0.0000</t>
+          <t>0.7170±0.0200</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7221±0.0306</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6599±0.0000</t>
+          <t>0.6608±0.0110</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6564±0.0000</t>
+          <t>0.6668±0.0055</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6564±0.0000</t>
+          <t>0.6668±0.0055</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6564±0.0000</t>
+          <t>0.6668±0.0055</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.6647±0.0112</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6993±0.0000</t>
+          <t>0.5897±0.0249</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6633±0.0000</t>
+          <t>0.6621±0.0033</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4713±0.0000</t>
+          <t>0.6815±0.0460</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6076±0.0000</t>
+          <t>0.5569±0.0342</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4752±0.0000</t>
+          <t>0.4888±0.0024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4279±0.0000</t>
+          <t>0.6034±0.0826</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.4895±0.0000</t>
+          <t>0.5028±0.0260</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.5459±0.0053</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5598±0.0000</t>
+          <t>0.5441±0.0212</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5347±0.0000</t>
+          <t>0.5325±0.0479</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5347±0.0000</t>
+          <t>0.5325±0.0479</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5347±0.0000</t>
+          <t>0.5325±0.0479</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5102±0.0000</t>
+          <t>0.5352±0.0171</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.4893±0.0000</t>
+          <t>0.4829±0.0223</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5445±0.0000</t>
+          <t>0.5733±0.0396</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6839±0.0000</t>
+          <t>0.6556±0.0304</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.5781±0.0000</t>
+          <t>0.5846±0.0259</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4657±0.0000</t>
+          <t>0.5151±0.0355</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.4290±0.0000</t>
+          <t>0.6097±0.0339</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5581±0.0000</t>
+          <t>0.5575±0.0285</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5777±0.0000</t>
+          <t>0.5446±0.0127</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.5989±0.0000</t>
+          <t>0.5720±0.0321</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.5889±0.0193</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.5889±0.0193</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.5919±0.0000</t>
+          <t>0.5889±0.0193</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.5609±0.0000</t>
+          <t>0.5789±0.0248</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4955±0.0000</t>
+          <t>0.4844±0.0049</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.5813±0.0000</t>
+          <t>0.6040±0.0176</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.6209±0.0384</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.5510±0.0000</t>
+          <t>0.5362±0.0176</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4941±0.0000</t>
+          <t>0.4954±0.0048</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4899±0.0074</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5497±0.0000</t>
+          <t>0.5179±0.0316</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5345±0.0000</t>
+          <t>0.5287±0.0576</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5931±0.0000</t>
+          <t>0.5256±0.0154</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5015±0.0000</t>
+          <t>0.5434±0.0265</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5015±0.0000</t>
+          <t>0.5434±0.0265</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5015±0.0000</t>
+          <t>0.5434±0.0265</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.5075±0.0184</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.5067±0.0000</t>
+          <t>0.4603±0.0048</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4990±0.0143</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6186±0.0000</t>
+          <t>0.6343±0.0385</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.5104±0.0000</t>
+          <t>0.5156±0.0164</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4718±0.0000</t>
+          <t>0.4905±0.0101</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4931±0.0000</t>
+          <t>0.5886±0.0843</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5086±0.0000</t>
+          <t>0.5171±0.0342</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5022±0.0000</t>
+          <t>0.5149±0.0314</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.5261±0.0000</t>
+          <t>0.5247±0.0150</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.4778±0.0000</t>
+          <t>0.5218±0.0143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.4778±0.0000</t>
+          <t>0.5218±0.0142</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.4778±0.0000</t>
+          <t>0.5219±0.0143</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.5101±0.0000</t>
+          <t>0.5280±0.0262</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.4954±0.0000</t>
+          <t>0.4785±0.0026</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.4982±0.0000</t>
+          <t>0.5452±0.0092</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6431±0.0000</t>
+          <t>0.7041±0.0344</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5639±0.0000</t>
+          <t>0.5720±0.0182</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4950±0.0000</t>
+          <t>0.5232±0.0549</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4975±0.0000</t>
+          <t>0.6991±0.0482</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6285±0.0000</t>
+          <t>0.5241±0.0285</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.4929±0.0000</t>
+          <t>0.5476±0.0109</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5967±0.0000</t>
+          <t>0.5858±0.0092</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.5460±0.0000</t>
+          <t>0.5383±0.0317</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.5460±0.0000</t>
+          <t>0.5383±0.0317</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.5460±0.0000</t>
+          <t>0.5383±0.0317</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5112±0.0000</t>
+          <t>0.5726±0.0167</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5122±0.0000</t>
+          <t>0.4879±0.0230</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.5741±0.0000</t>
+          <t>0.5610±0.0191</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.6979±0.0000</t>
+          <t>0.6927±0.0165</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5899±0.0000</t>
+          <t>0.5965±0.0091</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.4926±0.0000</t>
+          <t>0.5635±0.1008</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6145±0.0847</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.5420±0.0000</t>
+          <t>0.5252±0.0306</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.4426±0.0000</t>
+          <t>0.5289±0.0155</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5348±0.0000</t>
+          <t>0.5247±0.0386</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5398±0.0051</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5398±0.0051</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5398±0.0051</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5298±0.0000</t>
+          <t>0.5582±0.0185</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.5311±0.0000</t>
+          <t>0.5025±0.0140</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.5816±0.0000</t>
+          <t>0.5641±0.0248</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6645±0.0000</t>
+          <t>0.6394±0.0202</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.4475±0.0000</t>
+          <t>0.5141±0.0088</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4449±0.0000</t>
+          <t>0.4466±0.0121</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4231±0.0000</t>
+          <t>0.4064±0.0235</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5265±0.0000</t>
+          <t>0.5341±0.0097</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5056±0.0000</t>
+          <t>0.4903±0.0275</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.4439±0.0000</t>
+          <t>0.4891±0.0134</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5013±0.0000</t>
+          <t>0.5006±0.0219</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5013±0.0000</t>
+          <t>0.5006±0.0219</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5013±0.0000</t>
+          <t>0.5006±0.0219</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.4475±0.0000</t>
+          <t>0.5140±0.0020</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.4978±0.0000</t>
+          <t>0.4875±0.0160</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5199±0.0000</t>
+          <t>0.5259±0.0059</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5495±0.0000</t>
+          <t>0.7239±0.0384</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6598±0.0000</t>
+          <t>0.6320±0.0333</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5864±0.0000</t>
+          <t>0.5934±0.0019</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5630±0.0000</t>
+          <t>0.6957±0.0739</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5750±0.0000</t>
+          <t>0.5919±0.0328</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6335±0.0000</t>
+          <t>0.6368±0.0231</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6730±0.0000</t>
+          <t>0.6427±0.0423</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6164±0.0000</t>
+          <t>0.6150±0.0461</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6164±0.0000</t>
+          <t>0.6150±0.0461</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6164±0.0000</t>
+          <t>0.6150±0.0461</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6184±0.0000</t>
+          <t>0.6257±0.0342</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5877±0.0000</t>
+          <t>0.5816±0.0134</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6159±0.0000</t>
+          <t>0.6456±0.0375</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7238±0.0000</t>
+          <t>0.7041±0.0354</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.6405±0.0000</t>
+          <t>0.6507±0.0234</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5808±0.0000</t>
+          <t>0.6202±0.0357</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.7204±0.0217</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6744±0.0000</t>
+          <t>0.6400±0.0137</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.6272±0.0196</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6679±0.0000</t>
+          <t>0.6414±0.0246</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6504±0.0000</t>
+          <t>0.6571±0.0171</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6505±0.0000</t>
+          <t>0.6571±0.0171</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6504±0.0000</t>
+          <t>0.6571±0.0171</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6265±0.0000</t>
+          <t>0.6449±0.0166</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5938±0.0000</t>
+          <t>0.5931±0.0043</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6544±0.0000</t>
+          <t>0.6691±0.0148</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7523±0.0000</t>
+          <t>0.6752±0.0302</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6159±0.0000</t>
+          <t>0.6525±0.0254</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5966±0.0032</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5939±0.0036</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6425±0.0000</t>
+          <t>0.6114±0.0264</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6290±0.0000</t>
+          <t>0.6101±0.0333</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6580±0.0000</t>
+          <t>0.6306±0.0253</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.6462±0.0233</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.6462±0.0233</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.6462±0.0233</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6370±0.0000</t>
+          <t>0.6172±0.0202</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.6009±0.0000</t>
+          <t>0.5745±0.0041</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.6021±0.0079</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7055±0.0000</t>
+          <t>0.6971±0.0491</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6260±0.0000</t>
+          <t>0.6045±0.0266</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5851±0.0000</t>
+          <t>0.5943±0.0045</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5950±0.0000</t>
+          <t>0.6902±0.0731</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6195±0.0000</t>
+          <t>0.6103±0.0206</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6129±0.0000</t>
+          <t>0.6005±0.0132</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6228±0.0000</t>
+          <t>0.6424±0.0059</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5903±0.0000</t>
+          <t>0.6094±0.0165</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5903±0.0000</t>
+          <t>0.6093±0.0165</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5903±0.0000</t>
+          <t>0.6093±0.0165</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6141±0.0000</t>
+          <t>0.6366±0.0235</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5944±0.0000</t>
+          <t>0.5837±0.0085</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5963±0.0000</t>
+          <t>0.6322±0.0154</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7211±0.0000</t>
+          <t>0.7468±0.0372</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6055±0.0000</t>
+          <t>0.6531±0.0264</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.6295±0.0547</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.7712±0.0315</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6715±0.0000</t>
+          <t>0.6123±0.0159</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.5685±0.0000</t>
+          <t>0.6485±0.0286</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6692±0.0214</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.6602±0.0135</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.6602±0.0135</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.6602±0.0135</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.5888±0.0000</t>
+          <t>0.6461±0.0175</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.6049±0.0000</t>
+          <t>0.5909±0.0112</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6841±0.0000</t>
+          <t>0.6476±0.0069</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7281±0.0000</t>
+          <t>0.7338±0.0219</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6990±0.0000</t>
+          <t>0.6877±0.0074</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.6580±0.0916</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.6985±0.0719</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6341±0.0000</t>
+          <t>0.6106±0.0279</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5650±0.0000</t>
+          <t>0.6221±0.0182</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6677±0.0000</t>
+          <t>0.5913±0.0352</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6083±0.0061</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6083±0.0061</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6083±0.0061</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6494±0.0000</t>
+          <t>0.6307±0.0094</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6112±0.0000</t>
+          <t>0.5924±0.0091</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6826±0.0000</t>
+          <t>0.6290±0.0184</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7404±0.0000</t>
+          <t>0.7102±0.0145</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5706±0.0000</t>
+          <t>0.6184±0.0069</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5721±0.0000</t>
+          <t>0.5732±0.0069</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5631±0.0000</t>
+          <t>0.5493±0.0132</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6219±0.0000</t>
+          <t>0.6125±0.0044</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5988±0.0000</t>
+          <t>0.5857±0.0207</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5638±0.0000</t>
+          <t>0.5965±0.0151</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6038±0.0169</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6038±0.0169</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5968±0.0000</t>
+          <t>0.6038±0.0169</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5632±0.0000</t>
+          <t>0.6131±0.0029</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.5942±0.0142</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6123±0.0000</t>
+          <t>0.6240±0.0110</t>
         </is>
       </c>
     </row>
